--- a/Decks/Akiri.xlsx
+++ b/Decks/Akiri.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A7DCFA-A478-4F42-BCF0-B8AD2B5CE113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E83090-E439-4F2F-95F0-F53D7371DEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F514AF6-E090-4148-8D90-EA9B70B32839}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5F514AF6-E090-4148-8D90-EA9B70B32839}"/>
   </bookViews>
   <sheets>
     <sheet name="Akiri" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="111">
   <si>
     <t>Função</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>Zephyr Boots</t>
+  </si>
+  <si>
+    <t>https://www.ligamagic.com.br/?view=dks/deck&amp;id=10019724</t>
   </si>
 </sst>
 </file>
@@ -770,16 +773,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37116DFC-C63B-438F-A8B3-37523BEE0595}">
   <sheetPr codeName="Planilha26"/>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -798,8 +802,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -814,7 +821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -829,7 +836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -844,7 +851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -859,7 +866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -874,7 +881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -889,7 +896,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -904,7 +911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -919,7 +926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -934,7 +941,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -949,7 +956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -964,7 +971,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -979,7 +986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -994,7 +1001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1009,7 +1016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>

--- a/Decks/Akiri.xlsx
+++ b/Decks/Akiri.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E83090-E439-4F2F-95F0-F53D7371DEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889F69F8-7BEA-4F25-B6D2-205DDD05314F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5F514AF6-E090-4148-8D90-EA9B70B32839}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F514AF6-E090-4148-8D90-EA9B70B32839}"/>
   </bookViews>
   <sheets>
     <sheet name="Akiri" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="110">
   <si>
     <t>Função</t>
   </si>
@@ -366,9 +366,6 @@
   </si>
   <si>
     <t>Zephyr Boots</t>
-  </si>
-  <si>
-    <t>https://www.ligamagic.com.br/?view=dks/deck&amp;id=10019724</t>
   </si>
 </sst>
 </file>
@@ -773,17 +770,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37116DFC-C63B-438F-A8B3-37523BEE0595}">
   <sheetPr codeName="Planilha26"/>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,11 +798,8 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -821,7 +814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -836,7 +829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -851,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -866,7 +859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -881,7 +874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -896,7 +889,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -911,7 +904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -926,7 +919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -941,7 +934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -956,7 +949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -971,7 +964,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -986,7 +979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1001,7 +994,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1016,7 +1009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>

--- a/Decks/Akiri.xlsx
+++ b/Decks/Akiri.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889F69F8-7BEA-4F25-B6D2-205DDD05314F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133FDC86-8301-422C-8218-4051DABE249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F514AF6-E090-4148-8D90-EA9B70B32839}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="108">
   <si>
     <t>Função</t>
   </si>
@@ -218,9 +218,6 @@
     <t>Blasphemous Act</t>
   </si>
   <si>
-    <t>Shatter the Sky</t>
-  </si>
-  <si>
     <t>Day of Judgment</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>Sword of Once and Future</t>
   </si>
   <si>
-    <t>Glimmer Lens</t>
-  </si>
-  <si>
     <t>Sword of Light and Shadow</t>
   </si>
   <si>
@@ -296,9 +290,6 @@
     <t>Umezawa's Jitte</t>
   </si>
   <si>
-    <t>Horn of Valhalla // Ysgard's Call</t>
-  </si>
-  <si>
     <t>Lost Jitte</t>
   </si>
   <si>
@@ -326,9 +317,6 @@
     <t>Thran Power Suit</t>
   </si>
   <si>
-    <t>Cloak of the Bat</t>
-  </si>
-  <si>
     <t>Nettlecyst</t>
   </si>
   <si>
@@ -366,6 +354,12 @@
   </si>
   <si>
     <t>Zephyr Boots</t>
+  </si>
+  <si>
+    <t>Avenge</t>
+  </si>
+  <si>
+    <t>Kirol, Attentive First-Year</t>
   </si>
 </sst>
 </file>
@@ -958,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,10 +1658,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1814,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -1829,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -1844,473 +1838,473 @@
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="B72" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="F72"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F78"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F79"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F81"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E82" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B90" s="5" t="b">
         <f>C90&lt;&gt;D90</f>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B94" s="5" t="b">
         <f>C94&lt;&gt;D94</f>
         <v>1</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B98" s="5" t="b">
         <f>C98&lt;&gt;D98</f>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Akiri.xlsx
+++ b/Decks/Akiri.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133FDC86-8301-422C-8218-4051DABE249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7401D848-286B-4757-8F70-DF86C5254B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F514AF6-E090-4148-8D90-EA9B70B32839}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="106">
   <si>
     <t>Função</t>
   </si>
@@ -110,12 +110,6 @@
     <t>Zirda, the Dawnwaker</t>
   </si>
   <si>
-    <t>Danitha Capashen, Paragon</t>
-  </si>
-  <si>
-    <t>Cid, Freeflier Pilot</t>
-  </si>
-  <si>
     <t>Bureau Headmaster</t>
   </si>
   <si>
@@ -221,9 +215,6 @@
     <t>Day of Judgment</t>
   </si>
   <si>
-    <t>Kusari-Gama</t>
-  </si>
-  <si>
     <t>Chain Reaction</t>
   </si>
   <si>
@@ -281,9 +272,6 @@
     <t>Swiftfoot Boots</t>
   </si>
   <si>
-    <t>Plate Armor</t>
-  </si>
-  <si>
     <t>Lavaspur Boots</t>
   </si>
   <si>
@@ -360,6 +348,12 @@
   </si>
   <si>
     <t>Kirol, Attentive First-Year</t>
+  </si>
+  <si>
+    <t>Kili the Resourceful</t>
+  </si>
+  <si>
+    <t>Dwalin, Weaponmaster</t>
   </si>
 </sst>
 </file>
@@ -952,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1369,13 +1363,13 @@
       </c>
       <c r="B40" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1387,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F41"/>
     </row>
@@ -1403,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1433,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1448,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1463,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,833 +1472,833 @@
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="B48" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="b">
         <f>C55&lt;&gt;D55</f>
         <v>0</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B57" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="D57" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B62" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="D62" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="D66" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F72"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="B74" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F78"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F79"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F81"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E82" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B90" s="5" t="b">
         <f>C90&lt;&gt;D90</f>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B94" s="5" t="b">
         <f>C94&lt;&gt;D94</f>
         <v>1</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B98" s="5" t="b">
         <f>C98&lt;&gt;D98</f>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
